--- a/src/nodes/HPC/compressor_stage_9_blade_stator_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_9_blade_stator_coordinates_foil.xlsx
@@ -1023,7 +1023,7 @@
         <v>0.00073048849911674636</v>
       </c>
       <c r="B2">
-        <v>0.00048549017405926786</v>
+        <v>0.000539546322993907</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0014609769982334927</v>
       </c>
       <c r="B3">
-        <v>0.00079105179791034172</v>
+        <v>0.00086556162482024984</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0021914654973502392</v>
       </c>
       <c r="B4">
-        <v>0.0010614703566412952</v>
+        <v>0.001151758735132125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0029219539964669855</v>
       </c>
       <c r="B5">
-        <v>0.0013049191175923103</v>
+        <v>0.0014079179959677714</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0036524424955837317</v>
       </c>
       <c r="B6">
-        <v>0.0015247998106520232</v>
+        <v>0.0016380958605836517</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0043829309947004784</v>
       </c>
       <c r="B7">
-        <v>0.0017230954805451653</v>
+        <v>0.0018446487667981922</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0051134194938172251</v>
       </c>
       <c r="B8">
-        <v>0.0019010125840662306</v>
+        <v>0.0020290024071885769</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0058439079929339709</v>
       </c>
       <c r="B9">
-        <v>0.00206036518347485</v>
+        <v>0.0021933140903140982</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0065743964920507176</v>
       </c>
       <c r="B10">
-        <v>0.0022030986409131157</v>
+        <v>0.0023398998580981788</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.0073048849911674634</v>
       </c>
       <c r="B11">
-        <v>0.0023310759125878219</v>
+        <v>0.0024709790699386611</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.008035373490284211</v>
       </c>
       <c r="B12">
-        <v>0.0024453226735383611</v>
+        <v>0.0025877674111796319</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.0087658619894009568</v>
       </c>
       <c r="B13">
-        <v>0.0025435978800698146</v>
+        <v>0.0026875625534757428</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.0094963504885177026</v>
       </c>
       <c r="B14">
-        <v>0.0026245814880696584</v>
+        <v>0.0027687684032583243</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.01022683898763445</v>
       </c>
       <c r="B15">
-        <v>0.0026939041704892594</v>
+        <v>0.0028381318197548697</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.010957327486751194</v>
       </c>
       <c r="B16">
-        <v>0.002756730106195167</v>
+        <v>0.0029018407426266795</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.011687815985867942</v>
       </c>
       <c r="B17">
-        <v>0.0028094067806507766</v>
+        <v>0.0029555044804741261</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.012418304484984689</v>
       </c>
       <c r="B18">
-        <v>0.0028472014861225421</v>
+        <v>0.0029934372117088178</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.013148792984101435</v>
       </c>
       <c r="B19">
-        <v>0.0028698774354923126</v>
+        <v>0.0030153512250482334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.013879281483218181</v>
       </c>
       <c r="B20">
-        <v>0.0028783218217957843</v>
+        <v>0.0030223083367863189</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.014609769982334927</v>
       </c>
       <c r="B21">
-        <v>0.0028734218380686545</v>
+        <v>0.0030153703632170206</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.015340258481451674</v>
       </c>
       <c r="B22">
-        <v>0.0028559047117307033</v>
+        <v>0.0029954080818675268</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.016070746980568422</v>
       </c>
       <c r="B23">
-        <v>0.00282585780773804</v>
+        <v>0.0029625281151979942</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.016801235479685168</v>
       </c>
       <c r="B24">
-        <v>0.0027832085254308569</v>
+        <v>0.0029166460469018229</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.017531723978801914</v>
       </c>
       <c r="B25">
-        <v>0.0027278842641493477</v>
+        <v>0.0028576774606724107</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.018262212477918659</v>
       </c>
       <c r="B26">
-        <v>0.0026597823715991424</v>
+        <v>0.0027855027842792189</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.018992700977035405</v>
       </c>
       <c r="B27">
-        <v>0.0025786799889476208</v>
+        <v>0.0026998618217959512</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.019723189476152151</v>
       </c>
       <c r="B28">
-        <v>0.0024843242057276012</v>
+        <v>0.0026004592213723725</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.0204536779752689</v>
       </c>
       <c r="B29">
-        <v>0.0023764621114719022</v>
+        <v>0.0024869996311582482</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.021184166474385646</v>
       </c>
       <c r="B30">
-        <v>0.0022549518375731313</v>
+        <v>0.0023593219250421381</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.021914654973502389</v>
       </c>
       <c r="B31">
-        <v>0.0021200956828630498</v>
+        <v>0.0022178018798677829</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.022645143472619138</v>
       </c>
       <c r="B32">
-        <v>0.0019723069880332083</v>
+        <v>0.0020629494982177137</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.023375631971735884</v>
       </c>
       <c r="B33">
-        <v>0.0018119990937751564</v>
+        <v>0.0018952747826744656</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.024106120470852633</v>
       </c>
       <c r="B34">
-        <v>0.0016393925693510537</v>
+        <v>0.0017150575542488474</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.024836608969969379</v>
       </c>
       <c r="B35">
-        <v>0.0014539368983054939</v>
+        <v>0.0015216569076647688</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.025567097469086121</v>
       </c>
       <c r="B36">
-        <v>0.0012548887927536796</v>
+        <v>0.0013142017560744161</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.02629758596820287</v>
       </c>
       <c r="B37">
-        <v>0.0010415049648108115</v>
+        <v>0.001091821012629973</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.027028074467319616</v>
       </c>
       <c r="B38">
-        <v>0.00081257733485095446</v>
+        <v>0.0008530870219937035</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.027758562966436362</v>
       </c>
       <c r="B39">
-        <v>0.00056503865628361937</v>
+        <v>0.00059434585486818311</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.028489051465553111</v>
       </c>
       <c r="B40">
-        <v>0.00029535689077717862</v>
+        <v>0.00031138701346606571</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.028489051465553111</v>
       </c>
       <c r="B43">
-        <v>0.00013505566388830775</v>
+        <v>0.00011902554119942072</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.027758562966436362</v>
       </c>
       <c r="B44">
-        <v>0.00027196667043798123</v>
+        <v>0.00024265947185341747</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.027028074467319616</v>
       </c>
       <c r="B45">
-        <v>0.0004074804634234648</v>
+        <v>0.00036697077628071581</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.02629758596820287</v>
       </c>
       <c r="B46">
-        <v>0.00053834448661919661</v>
+        <v>0.0004880284388000351</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.025567097469086121</v>
       </c>
       <c r="B47">
-        <v>0.0006617591595463136</v>
+        <v>0.00060244619622557688</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.024836608969969379</v>
       </c>
       <c r="B48">
-        <v>0.00077673680471274488</v>
+        <v>0.00070901679535346985</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.024106120470852633</v>
       </c>
       <c r="B49">
-        <v>0.00088274272037311961</v>
+        <v>0.00080707773547532616</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.023375631971735884</v>
       </c>
       <c r="B50">
-        <v>0.00097924220478206561</v>
+        <v>0.00089596651588275643</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.022645143472619138</v>
       </c>
       <c r="B51">
-        <v>0.0010658818861881533</v>
+        <v>0.00097523937600364785</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.021914654973502389</v>
       </c>
       <c r="B52">
-        <v>0.0011430337128157232</v>
+        <v>0.0010453275158109907</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.021184166474385646</v>
       </c>
       <c r="B53">
-        <v>0.0012112509628830583</v>
+        <v>0.0011068808754140511</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.0204536779752689</v>
       </c>
       <c r="B54">
-        <v>0.001271086914608442</v>
+        <v>0.001160549394922096</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.019723189476152151</v>
       </c>
       <c r="B55">
-        <v>0.0013229740492798846</v>
+        <v>0.0012068390336351133</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.018992700977035405</v>
       </c>
       <c r="B56">
-        <v>0.0013668616604643102</v>
+        <v>0.0012456798276159792</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.018262212477918659</v>
       </c>
       <c r="B57">
-        <v>0.0014025782447983691</v>
+        <v>0.001276857832118292</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.017531723978801914</v>
       </c>
       <c r="B58">
-        <v>0.0014299522989187129</v>
+        <v>0.0013001591023956496</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.016801235479685168</v>
       </c>
       <c r="B59">
-        <v>0.0014488333107211967</v>
+        <v>0.0013153957892502307</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.016070746980568422</v>
       </c>
       <c r="B60">
-        <v>0.001459154733138489</v>
+        <v>0.0013224844256785344</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.015340258481451674</v>
       </c>
       <c r="B61">
-        <v>0.0014608710103624636</v>
+        <v>0.0013213676402256398</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.014609769982334927</v>
       </c>
       <c r="B62">
-        <v>0.0014539365865849931</v>
+        <v>0.0013119880614366271</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.013879281483218181</v>
       </c>
       <c r="B63">
-        <v>0.001438456671890437</v>
+        <v>0.0012944701568999026</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.013148792984101435</v>
       </c>
       <c r="B64">
-        <v>0.0014151395399331038</v>
+        <v>0.001269665750377183</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.012418304484984689</v>
       </c>
       <c r="B65">
-        <v>0.0013848442302597879</v>
+        <v>0.0012386085046735124</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.011687815985867942</v>
       </c>
       <c r="B66">
-        <v>0.0013484297824172841</v>
+        <v>0.0012023320825939349</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.010957327486751194</v>
       </c>
       <c r="B67">
-        <v>0.0013056237418800451</v>
+        <v>0.0011605131054485331</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.01022683898763445</v>
       </c>
       <c r="B68">
-        <v>0.001251627677833155</v>
+        <v>0.0011074000285675447</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.0094963504885177026</v>
       </c>
       <c r="B69">
-        <v>0.0011827123361829979</v>
+        <v>0.0010385254209943321</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.0087658619894009568</v>
       </c>
       <c r="B70">
-        <v>0.0011039511460105306</v>
+        <v>0.0009599864726046025</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.008035373490284211</v>
       </c>
       <c r="B71">
-        <v>0.001020875297125648</v>
+        <v>0.00087843055948437683</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.0073048849911674634</v>
       </c>
       <c r="B72">
-        <v>0.000932044339079429</v>
+        <v>0.00079214118172858986</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0065743964920507176</v>
       </c>
       <c r="B73">
-        <v>0.00083508646906248489</v>
+        <v>0.0006982852518774219</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0058439079929339709</v>
       </c>
       <c r="B74">
-        <v>0.00073087611508237168</v>
+        <v>0.00059792720824312386</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0051134194938172251</v>
       </c>
       <c r="B75">
-        <v>0.00062111435284276843</v>
+        <v>0.0004931245297204221</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0043829309947004784</v>
       </c>
       <c r="B76">
-        <v>0.00050756261801489938</v>
+        <v>0.00038600933176187279</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0036524424955837317</v>
       </c>
       <c r="B77">
-        <v>0.00039183931133573703</v>
+        <v>0.00027854326140410845</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0029219539964669855</v>
       </c>
       <c r="B78">
-        <v>0.00027493033383769794</v>
+        <v>0.00017193145546223681</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0021914654973502392</v>
       </c>
       <c r="B79">
-        <v>0.00015858657173299662</v>
+        <v>6.8298193242166832E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0014609769982334927</v>
       </c>
       <c r="B80">
-        <v>4.5953528811260635E-05</v>
+        <v>-2.855629809864745E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.00073048849911674636</v>
       </c>
       <c r="B81">
-        <v>-5.5071315287124467E-05</v>
+        <v>-0.00010912746422176368</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.00079363154813975032</v>
       </c>
       <c r="B2">
-        <v>0.00064876030156697177</v>
+        <v>0.00076621777069165462</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0015872630962795007</v>
       </c>
       <c r="B3">
-        <v>0.0010287799790684876</v>
+        <v>0.0011906808148889965</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0023808946444192512</v>
       </c>
       <c r="B4">
-        <v>0.001360223759828322</v>
+        <v>0.0015564094785284683</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0031745261925590013</v>
       </c>
       <c r="B5">
-        <v>0.0016554711025061728</v>
+        <v>0.0018792751990815821</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0039681577406987514</v>
       </c>
       <c r="B6">
-        <v>0.0019196475007553792</v>
+        <v>0.00216582610483765</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0047617892888385024</v>
       </c>
       <c r="B7">
-        <v>0.0021557250784812647</v>
+        <v>0.0024198456577021734</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0055554208369782525</v>
       </c>
       <c r="B8">
-        <v>0.0023654969224674739</v>
+        <v>0.002643603317280095</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0063490523851180026</v>
       </c>
       <c r="B9">
-        <v>0.002551684955343221</v>
+        <v>0.0028405668388660904</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0071426839332577527</v>
       </c>
       <c r="B10">
-        <v>0.00271721301289217</v>
+        <v>0.0030144655005446335</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.0079363154813975028</v>
       </c>
       <c r="B11">
-        <v>0.0028648837476702113</v>
+        <v>0.0031688763758696615</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.0087299470295372546</v>
       </c>
       <c r="B12">
-        <v>0.0029962283052251083</v>
+        <v>0.0033057434797837573</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.0095235785776770047</v>
       </c>
       <c r="B13">
-        <v>0.0031078129862998757</v>
+        <v>0.00342063079731464</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.010317210125816755</v>
       </c>
       <c r="B14">
-        <v>0.0031976069145688161</v>
+        <v>0.003510907630079157</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.011110841673956505</v>
       </c>
       <c r="B15">
-        <v>0.0032741553502361256</v>
+        <v>0.0035875445759655502</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.011904473222096253</v>
       </c>
       <c r="B16">
-        <v>0.0033452956754254693</v>
+        <v>0.0036606035253969166</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.012698104770236005</v>
       </c>
       <c r="B17">
-        <v>0.0034054576234084947</v>
+        <v>0.0037229102426643949</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.013491736318375757</v>
       </c>
       <c r="B18">
-        <v>0.00344743004868298</v>
+        <v>0.0037651825812162185</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.014285367866515505</v>
       </c>
       <c r="B19">
-        <v>0.0034708459395032397</v>
+        <v>0.0037869428772609685</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.015078999414655257</v>
       </c>
       <c r="B20">
-        <v>0.0034770493175627238</v>
+        <v>0.003789914587697312</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.015872630962795006</v>
       </c>
       <c r="B21">
-        <v>0.0034673842045548826</v>
+        <v>0.003775821169423915</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.016666262510934757</v>
       </c>
       <c r="B22">
-        <v>0.003442953080838914</v>
+        <v>0.0037460770198092545</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.017459894059074509</v>
       </c>
       <c r="B23">
-        <v>0.0034038922614370083</v>
+        <v>0.0037008602981010458</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.018253525607214258</v>
       </c>
       <c r="B24">
-        <v>0.003350096520037104</v>
+        <v>0.0036400401040168132</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.019047157155354009</v>
       </c>
       <c r="B25">
-        <v>0.00328146063032714</v>
+        <v>0.0035634855372740815</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.019840788703493758</v>
       </c>
       <c r="B26">
-        <v>0.0031978353951615272</v>
+        <v>0.0034710106357538147</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.02063442025163351</v>
       </c>
       <c r="B27">
-        <v>0.0030988957340605723</v>
+        <v>0.0033622091899907329</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.021428051799773258</v>
       </c>
       <c r="B28">
-        <v>0.0029842725957110539</v>
+        <v>0.003236619928682996</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.02222168334791301</v>
       </c>
       <c r="B29">
-        <v>0.0028535969287997506</v>
+        <v>0.0030937815805287638</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.023015314896052762</v>
       </c>
       <c r="B30">
-        <v>0.0027066704380940112</v>
+        <v>0.00293345400606986</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.023808946444192507</v>
       </c>
       <c r="B31">
-        <v>0.0025439778526834614</v>
+        <v>0.0027562815932227641</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.024602577992332259</v>
       </c>
       <c r="B32">
-        <v>0.0023661746577382926</v>
+        <v>0.0025631298617476176</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.02539620954047201</v>
       </c>
       <c r="B33">
-        <v>0.0021739163384286997</v>
+        <v>0.0023548643314045634</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.026189841088611762</v>
       </c>
       <c r="B34">
-        <v>0.001967567327281023</v>
+        <v>0.0021319781815984143</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.026983472636751514</v>
       </c>
       <c r="B35">
-        <v>0.0017463278462461845</v>
+        <v>0.001893475230312666</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.027777104184891259</v>
       </c>
       <c r="B36">
-        <v>0.0015091070646312552</v>
+        <v>0.0016379869551754844</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.028570735733031011</v>
       </c>
       <c r="B37">
-        <v>0.0012548141517433015</v>
+        <v>0.0013641448338150334</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.029364367281170763</v>
       </c>
       <c r="B38">
-        <v>0.00098165351792685253</v>
+        <v>0.0010696761651297309</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.030157998829310514</v>
       </c>
       <c r="B39">
-        <v>0.00068501053767627189</v>
+        <v>0.00074869153309900537</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.030951630377450263</v>
       </c>
       <c r="B40">
-        <v>0.00035956582652338213</v>
+        <v>0.00039439734297253682</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.030951630377450263</v>
       </c>
       <c r="B43">
-        <v>0.00011574521137929999</v>
+        <v>8.0913694930145386E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.030157998829310514</v>
       </c>
       <c r="B44">
-        <v>0.00023924356971713787</v>
+        <v>0.00017556257429440444</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.029364367281170763</v>
       </c>
       <c r="B45">
-        <v>0.00036549498750670277</v>
+        <v>0.00027747234030382431</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.028570735733031011</v>
       </c>
       <c r="B46">
-        <v>0.00048949937724117733</v>
+        <v>0.00038016869516944546</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.027777104184891259</v>
       </c>
       <c r="B47">
-        <v>0.00060694783082164785</v>
+        <v>0.00047806794027741836</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.026983472636751514</v>
       </c>
       <c r="B48">
-        <v>0.00071629615778081484</v>
+        <v>0.00056914877371433339</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.026189841088611762</v>
       </c>
       <c r="B49">
-        <v>0.00081669134705928358</v>
+        <v>0.0006522804927418923</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.02539620954047201</v>
       </c>
       <c r="B50">
-        <v>0.0009072803875976584</v>
+        <v>0.00072633239462179542</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.024602577992332259</v>
       </c>
       <c r="B51">
-        <v>0.000987488229673018</v>
+        <v>0.00079053302566369312</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.023808946444192507</v>
       </c>
       <c r="B52">
-        <v>0.0010578516689083372</v>
+        <v>0.00084554792836903409</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.023015314896052762</v>
       </c>
       <c r="B53">
-        <v>0.0011191854622630655</v>
+        <v>0.00089240189428721635</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.02222168334791301</v>
       </c>
       <c r="B54">
-        <v>0.0011723043666966523</v>
+        <v>0.00093211971496763861</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.021428051799773258</v>
       </c>
       <c r="B55">
-        <v>0.0012178412649074529</v>
+        <v>0.00096549393193551</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.02063442025163351</v>
       </c>
       <c r="B56">
-        <v>0.0012557015425494458</v>
+        <v>0.000992388086619285</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.019840788703493758</v>
       </c>
       <c r="B57">
-        <v>0.0012856087110155164</v>
+        <v>0.0010124334704232289</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.019047157155354009</v>
       </c>
       <c r="B58">
-        <v>0.0013072862816985488</v>
+        <v>0.0010252613747516069</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.018253525607214258</v>
       </c>
       <c r="B59">
-        <v>0.0013204914321791415</v>
+        <v>0.0010305478481994325</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.017459894059074509</v>
       </c>
       <c r="B60">
-        <v>0.0013251160047887468</v>
+        <v>0.0010281479681247094</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.016666262510934757</v>
       </c>
       <c r="B61">
-        <v>0.0013210855080465294</v>
+        <v>0.0010179615690761889</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.015872630962795006</v>
       </c>
       <c r="B62">
-        <v>0.0013083254504716547</v>
+        <v>0.00099988848560262212</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.015078999414655257</v>
       </c>
       <c r="B63">
-        <v>0.001286992426620605</v>
+        <v>0.00097412715648601672</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.014285367866515505</v>
       </c>
       <c r="B64">
-        <v>0.0012581673751991323</v>
+        <v>0.00094207043744140291</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.013491736318375757</v>
       </c>
       <c r="B65">
-        <v>0.0012231623209503055</v>
+        <v>0.00090540978841706658</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.012698104770236005</v>
       </c>
       <c r="B66">
-        <v>0.0011832892886171939</v>
+        <v>0.000865836669361294</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.011904473222096253</v>
       </c>
       <c r="B67">
-        <v>0.0011381407256253367</v>
+        <v>0.00082283287565388915</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.011110841673956505</v>
       </c>
       <c r="B68">
-        <v>0.0010804307701301533</v>
+        <v>0.0007670415444007287</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.010317210125816755</v>
       </c>
       <c r="B69">
-        <v>0.0010045019059964286</v>
+        <v>0.00069120119048608774</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.0095235785776770047</v>
       </c>
       <c r="B70">
-        <v>0.00091808830919652815</v>
+        <v>0.00060527049818176438</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.0087299470295372546</v>
       </c>
       <c r="B71">
-        <v>0.00082962208331456458</v>
+        <v>0.00052010690875591557</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.0079363154813975028</v>
       </c>
       <c r="B72">
-        <v>0.00073693535027406212</v>
+        <v>0.00043294272207461236</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0071426839332577527</v>
       </c>
       <c r="B73">
-        <v>0.00063644559932492164</v>
+        <v>0.00033919311167245774</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0063490523851180026</v>
       </c>
       <c r="B74">
-        <v>0.0005295117706831373</v>
+        <v>0.00024062988716026828</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0055554208369782525</v>
       </c>
       <c r="B75">
-        <v>0.00041875215877912596</v>
+        <v>0.000140645763966505</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0047617892888385024</v>
       </c>
       <c r="B76">
-        <v>0.00030688102393490208</v>
+        <v>4.2760444713993377E-05</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0039681577406987514</v>
       </c>
       <c r="B77">
-        <v>0.00019639727217948363</v>
+        <v>-4.9781331902786989E-05</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0031745261925590013</v>
       </c>
       <c r="B78">
-        <v>8.8842426478305973E-05</v>
+        <v>-0.00013496167009710341</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0023808946444192512</v>
       </c>
       <c r="B79">
-        <v>-1.3076271072702176E-05</v>
+        <v>-0.00020926198977284829</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0015872630962795007</v>
       </c>
       <c r="B80">
-        <v>-0.00010452587167507571</v>
+        <v>-0.00026642670749558469</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.00079363154813975032</v>
       </c>
       <c r="B81">
-        <v>-0.00017344198230580967</v>
+        <v>-0.0002908994514304926</v>
       </c>
     </row>
     <row r="82" spans="1:2">
